--- a/BRIN 3219/Junio/BRIN3219-EXPENSAS-JUNIO.xlsx
+++ b/BRIN 3219/Junio/BRIN3219-EXPENSAS-JUNIO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BRIN 3219\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BEDCC41-E104-4092-A6FF-E23FC20DFA93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E50F1671-A128-45D8-96B9-7B8608B109CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Planilla!$A$1:$N$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">RESUMEN!$A$1:$H$103</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">RESUMEN!$A$1:$H$98</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="154">
   <si>
     <t>U.F.</t>
   </si>
@@ -240,12 +240,6 @@
     <t>EXPENSAS</t>
   </si>
   <si>
-    <t>Sueldo Sra Monica Forment</t>
-  </si>
-  <si>
-    <t>AFIP NO SE PAGA HASTA RESOLVER LA SITUACION CUENTA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lema ascensores abono mantenimiento </t>
   </si>
   <si>
@@ -307,12 +301,6 @@
   </si>
   <si>
     <t>Deducciones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plus antigüedad </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plus retiro residuos </t>
   </si>
   <si>
     <t>2-CARGAS SOCIALES</t>
@@ -462,9 +450,6 @@
     <t>Eliseo</t>
   </si>
   <si>
-    <t>Asignacion remunerativa</t>
-  </si>
-  <si>
     <t>Ingreso por pago de Expensas - MARZO</t>
   </si>
   <si>
@@ -495,24 +480,9 @@
     <t>GASTOS EXTR. ASCENSOR Y LIBROS</t>
   </si>
   <si>
-    <t>Ezequiel Sarro - escrito presentado ante la camara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julio doartero - visitas de emergencia falta de agua </t>
-  </si>
-  <si>
     <t>Horas extra fumigacion</t>
   </si>
   <si>
-    <t>Acuerdo banco galicia con el estudio palmero de belizan y asociados por el embargo de la cuenta realizado por la Sra. Elena Graciela</t>
-  </si>
-  <si>
-    <t>Colocacion ceramicos en el 1er piso - Fernando Parra</t>
-  </si>
-  <si>
-    <t>EN MAY LOS CERRAMOS ADEUDANDO LOS SINDICATOS YA QUE SE NOS PASO PAGARLOS</t>
-  </si>
-  <si>
     <t>VTO: 14/07</t>
   </si>
   <si>
@@ -525,10 +495,16 @@
     <t>Egresos por gastos mes - JUNIO</t>
   </si>
   <si>
-    <t>Kromacolor - membraba liquida para techos y muros rojo</t>
-  </si>
-  <si>
     <t>AYSA - Vto 02/06</t>
+  </si>
+  <si>
+    <t>Sueldo Sra Monica Forment y SAC</t>
+  </si>
+  <si>
+    <t>ARCA NO SE PAGA HASTA RESOLVER LA SITUACION CUENTA</t>
+  </si>
+  <si>
+    <t>Kromacolor - membrana liquida para techos</t>
   </si>
 </sst>
 </file>
@@ -545,7 +521,7 @@
     <numFmt numFmtId="169" formatCode="0.0"/>
     <numFmt numFmtId="170" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -750,23 +726,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -815,6 +776,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEE0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="42">
     <border>
@@ -1339,7 +1306,7 @@
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="234">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1635,8 +1602,8 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="21" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="167" fontId="17" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="21" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1781,9 +1748,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="30" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="31" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="21" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2306,7 +2270,7 @@
       <c r="J3" s="118"/>
       <c r="K3" s="118"/>
       <c r="L3" s="61" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M3" s="61"/>
       <c r="N3" s="61"/>
@@ -2314,24 +2278,21 @@
     <row r="4" spans="1:14" ht="18.75" customHeight="1">
       <c r="A4" s="119"/>
       <c r="B4" s="120" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C4" s="61"/>
       <c r="D4" s="61"/>
       <c r="E4" s="120" t="s">
-        <v>85</v>
-      </c>
-      <c r="F4" s="124">
-        <f>105400+260-8</f>
-        <v>105652</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="F4" s="124"/>
       <c r="G4" s="118"/>
       <c r="H4" s="118"/>
       <c r="I4" s="118"/>
       <c r="J4" s="118"/>
       <c r="K4" s="118"/>
       <c r="L4" s="61" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="M4" s="61"/>
       <c r="N4" s="61"/>
@@ -2360,12 +2321,12 @@
     <row r="6" spans="1:14" ht="15.75" customHeight="1">
       <c r="A6" s="121"/>
       <c r="B6" s="123" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C6" s="21"/>
       <c r="D6" s="21"/>
       <c r="E6" s="120" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="F6" s="115"/>
       <c r="G6" s="115"/>
@@ -2406,7 +2367,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="112" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" s="110" t="s">
         <v>2</v>
@@ -2421,19 +2382,19 @@
         <v>64</v>
       </c>
       <c r="I8" s="113" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="J8" s="113" t="s">
         <v>65</v>
       </c>
       <c r="K8" s="127" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L8" s="110" t="s">
         <v>7</v>
       </c>
       <c r="M8" s="110" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="N8" s="114" t="s">
         <v>8</v>
@@ -2450,17 +2411,17 @@
         <v>19</v>
       </c>
       <c r="D9" s="176" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E9" s="177">
         <v>4.0500000000000001E-2</v>
       </c>
       <c r="F9" s="99">
-        <v>654594.59569455055</v>
+        <v>153594.22216499998</v>
       </c>
       <c r="G9" s="180">
         <f>F9</f>
-        <v>654594.59569455055</v>
+        <v>153594.22216499998</v>
       </c>
       <c r="H9" s="68">
         <f>IF(F9&gt;G9,F9-G9,0)</f>
@@ -2476,7 +2437,7 @@
       </c>
       <c r="K9" s="68">
         <f>F$4*E9</f>
-        <v>4278.9059999999999</v>
+        <v>0</v>
       </c>
       <c r="L9" s="178">
         <f>B$5*E9</f>
@@ -2488,7 +2449,7 @@
       </c>
       <c r="N9" s="178">
         <f>H9+I9-J9+K9+L9+M9</f>
-        <v>153594.22216499998</v>
+        <v>149315.316165</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -2526,7 +2487,7 @@
       </c>
       <c r="K10" s="24">
         <f t="shared" ref="K10:K31" si="2">F$4*E10</f>
-        <v>6846.2495999999992</v>
+        <v>0</v>
       </c>
       <c r="L10" s="25">
         <f t="shared" ref="L10:L31" si="3">B$5*E10</f>
@@ -2538,7 +2499,7 @@
       </c>
       <c r="N10" s="25">
         <f t="shared" ref="N10:N31" si="5">H10+I10-J10+K10+L10+M10</f>
-        <v>245750.75546399999</v>
+        <v>238904.50586400001</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1">
@@ -2552,17 +2513,17 @@
         <v>21</v>
       </c>
       <c r="D11" s="176" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E11" s="177">
         <v>4.82E-2</v>
       </c>
       <c r="F11" s="99">
-        <v>787860.93475176918</v>
+        <v>181861.02137776918</v>
       </c>
       <c r="G11" s="160">
-        <f>606000+182796</f>
-        <v>788796</v>
+        <f>F11</f>
+        <v>181861.02137776918</v>
       </c>
       <c r="H11" s="68">
         <f t="shared" si="0"/>
@@ -2574,11 +2535,11 @@
       </c>
       <c r="J11" s="68">
         <f t="shared" si="1"/>
-        <v>935.06524823082145</v>
+        <v>0</v>
       </c>
       <c r="K11" s="68">
         <f t="shared" si="2"/>
-        <v>5092.4264000000003</v>
+        <v>0</v>
       </c>
       <c r="L11" s="178">
         <f t="shared" si="3"/>
@@ -2590,7 +2551,7 @@
       </c>
       <c r="N11" s="178">
         <f>H11+I11-J11+K11+L11+M11+E7</f>
-        <v>181861.02137776918</v>
+        <v>177703.66022600001</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1">
@@ -2601,25 +2562,25 @@
         <v>43</v>
       </c>
       <c r="C12" s="157" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D12" s="157" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E12" s="158">
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F12" s="151">
-        <v>1322857.8579191184</v>
+        <v>1574699.6699171257</v>
       </c>
       <c r="G12" s="161"/>
       <c r="H12" s="152">
         <f t="shared" si="0"/>
-        <v>1322857.8579191184</v>
+        <v>1574699.6699171257</v>
       </c>
       <c r="I12" s="152">
         <f t="shared" si="6"/>
-        <v>48945.740743007387</v>
+        <v>58263.887786933657</v>
       </c>
       <c r="J12" s="152">
         <f t="shared" si="1"/>
@@ -2627,7 +2588,7 @@
       </c>
       <c r="K12" s="152">
         <f t="shared" si="2"/>
-        <v>5652.3819999999996</v>
+        <v>0</v>
       </c>
       <c r="L12" s="153">
         <f t="shared" si="3"/>
@@ -2639,7 +2600,7 @@
       </c>
       <c r="N12" s="153">
         <f t="shared" si="5"/>
-        <v>1574699.6699171257</v>
+        <v>1830207.2469590595</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1">
@@ -2659,17 +2620,14 @@
       <c r="F13" s="17">
         <v>146009.32230499998</v>
       </c>
-      <c r="G13" s="160">
-        <f>F13</f>
-        <v>146009.32230499998</v>
-      </c>
+      <c r="G13" s="160"/>
       <c r="H13" s="24">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>146009.32230499998</v>
       </c>
       <c r="I13" s="24">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>5402.3449252849996</v>
       </c>
       <c r="J13" s="24">
         <f t="shared" si="1"/>
@@ -2677,7 +2635,7 @@
       </c>
       <c r="K13" s="24">
         <f t="shared" si="2"/>
-        <v>4067.6019999999999</v>
+        <v>0</v>
       </c>
       <c r="L13" s="25">
         <f t="shared" si="3"/>
@@ -2689,7 +2647,7 @@
       </c>
       <c r="N13" s="25">
         <f t="shared" si="5"/>
-        <v>146009.32230499998</v>
+        <v>293353.38753528497</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1">
@@ -2703,7 +2661,7 @@
         <v>24</v>
       </c>
       <c r="D14" s="93" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E14" s="45">
         <v>3.5900000000000001E-2</v>
@@ -2729,7 +2687,7 @@
       </c>
       <c r="K14" s="24">
         <f t="shared" si="2"/>
-        <v>3792.9068000000002</v>
+        <v>0</v>
       </c>
       <c r="L14" s="25">
         <f t="shared" si="3"/>
@@ -2741,7 +2699,7 @@
       </c>
       <c r="N14" s="25">
         <f t="shared" si="5"/>
-        <v>136148.952487</v>
+        <v>132356.04568700001</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -2755,24 +2713,24 @@
         <v>25</v>
       </c>
       <c r="D15" s="93" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E15" s="45">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F15" s="17">
-        <v>157007.42710199999</v>
+        <v>157015.12900677399</v>
       </c>
       <c r="G15" s="160">
         <v>157000</v>
       </c>
       <c r="H15" s="24">
         <f t="shared" si="0"/>
-        <v>7.4271019999869168</v>
+        <v>15.129006773990113</v>
       </c>
       <c r="I15" s="24">
         <f t="shared" si="6"/>
-        <v>0.27480277399951597</v>
+        <v>0.55977325063763428</v>
       </c>
       <c r="J15" s="24">
         <f t="shared" si="1"/>
@@ -2780,7 +2738,7 @@
       </c>
       <c r="K15" s="24">
         <f t="shared" si="2"/>
-        <v>4373.9928</v>
+        <v>0</v>
       </c>
       <c r="L15" s="25">
         <f t="shared" si="3"/>
@@ -2792,7 +2750,7 @@
       </c>
       <c r="N15" s="25">
         <f t="shared" si="5"/>
-        <v>157015.12900677399</v>
+        <v>152649.12308202463</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -2803,10 +2761,10 @@
         <v>47</v>
       </c>
       <c r="C16" s="94" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D16" s="93" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E16" s="45">
         <v>5.3499999999999999E-2</v>
@@ -2832,7 +2790,7 @@
       </c>
       <c r="K16" s="24">
         <f t="shared" si="2"/>
-        <v>5652.3819999999996</v>
+        <v>0</v>
       </c>
       <c r="L16" s="25">
         <f t="shared" si="3"/>
@@ -2844,7 +2802,7 @@
       </c>
       <c r="N16" s="25">
         <f t="shared" si="5"/>
-        <v>202896.07125499999</v>
+        <v>197243.68925499998</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="15" customHeight="1">
@@ -2858,7 +2816,7 @@
         <v>26</v>
       </c>
       <c r="D17" s="93" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E17" s="45">
         <v>3.85E-2</v>
@@ -2884,7 +2842,7 @@
       </c>
       <c r="K17" s="24">
         <f t="shared" si="2"/>
-        <v>4067.6019999999999</v>
+        <v>0</v>
       </c>
       <c r="L17" s="25">
         <f t="shared" si="3"/>
@@ -2896,7 +2854,7 @@
       </c>
       <c r="N17" s="25">
         <f t="shared" si="5"/>
-        <v>146009.32230499998</v>
+        <v>141941.720305</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="15" customHeight="1">
@@ -2914,18 +2872,16 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F18" s="151">
-        <v>1037840.4322724235</v>
-      </c>
-      <c r="G18" s="161">
-        <v>400000</v>
-      </c>
+        <v>797589.48075350327</v>
+      </c>
+      <c r="G18" s="161"/>
       <c r="H18" s="152">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
-        <v>637840.43227242352</v>
+        <v>797589.48075350327</v>
       </c>
       <c r="I18" s="152">
         <f t="shared" si="6"/>
-        <v>23600.095994079675</v>
+        <v>29510.810787879625</v>
       </c>
       <c r="J18" s="152">
         <f t="shared" si="1"/>
@@ -2933,7 +2889,7 @@
       </c>
       <c r="K18" s="152">
         <f t="shared" si="2"/>
-        <v>3792.9068000000002</v>
+        <v>0</v>
       </c>
       <c r="L18" s="153">
         <f t="shared" si="3"/>
@@ -2945,7 +2901,7 @@
       </c>
       <c r="N18" s="153">
         <f t="shared" si="5"/>
-        <v>797589.48075350327</v>
+        <v>959456.33722838294</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="15" customHeight="1">
@@ -2959,22 +2915,22 @@
         <v>28</v>
       </c>
       <c r="D19" s="157" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E19" s="158">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F19" s="151">
-        <v>797425.60751237522</v>
+        <v>983937.78209233307</v>
       </c>
       <c r="G19" s="161"/>
       <c r="H19" s="152">
         <f t="shared" si="0"/>
-        <v>797425.60751237522</v>
+        <v>983937.78209233307</v>
       </c>
       <c r="I19" s="152">
         <f t="shared" si="6"/>
-        <v>29504.747477957888</v>
+        <v>36405.697937416327</v>
       </c>
       <c r="J19" s="152">
         <f t="shared" si="1"/>
@@ -2982,7 +2938,7 @@
       </c>
       <c r="K19" s="152">
         <f t="shared" si="2"/>
-        <v>4373.9928</v>
+        <v>0</v>
       </c>
       <c r="L19" s="153">
         <f t="shared" si="3"/>
@@ -2994,7 +2950,7 @@
       </c>
       <c r="N19" s="153">
         <f t="shared" si="5"/>
-        <v>983937.78209233307</v>
+        <v>1172976.9143317495</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="15" customHeight="1">
@@ -3005,10 +2961,10 @@
         <v>51</v>
       </c>
       <c r="C20" s="101" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D20" s="97" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E20" s="46">
         <v>5.3499999999999999E-2</v>
@@ -3034,7 +2990,7 @@
       </c>
       <c r="K20" s="24">
         <f t="shared" si="2"/>
-        <v>5652.3819999999996</v>
+        <v>0</v>
       </c>
       <c r="L20" s="25">
         <f t="shared" si="3"/>
@@ -3046,7 +3002,7 @@
       </c>
       <c r="N20" s="25">
         <f t="shared" si="5"/>
-        <v>202896.07125499999</v>
+        <v>197243.68925499998</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="15" customHeight="1">
@@ -3060,22 +3016,25 @@
         <v>30</v>
       </c>
       <c r="D21" s="155" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E21" s="156">
         <v>3.85E-2</v>
       </c>
       <c r="F21" s="151">
-        <v>468960.78194434626</v>
-      </c>
-      <c r="G21" s="161"/>
+        <v>632321.65318128711</v>
+      </c>
+      <c r="G21" s="182">
+        <f>72641.6*2</f>
+        <v>145283.20000000001</v>
+      </c>
       <c r="H21" s="152">
         <f t="shared" si="0"/>
-        <v>468960.78194434626</v>
+        <v>487038.4531812871</v>
       </c>
       <c r="I21" s="152">
         <f t="shared" si="6"/>
-        <v>17351.548931940815</v>
+        <v>18020.422767707627</v>
       </c>
       <c r="J21" s="152">
         <f t="shared" si="1"/>
@@ -3083,7 +3042,7 @@
       </c>
       <c r="K21" s="152">
         <f t="shared" si="2"/>
-        <v>4067.6019999999999</v>
+        <v>0</v>
       </c>
       <c r="L21" s="153">
         <f t="shared" si="3"/>
@@ -3095,7 +3054,7 @@
       </c>
       <c r="N21" s="153">
         <f t="shared" si="5"/>
-        <v>632321.65318128711</v>
+        <v>647000.59625399474</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="15" customHeight="1">
@@ -3109,7 +3068,7 @@
         <v>31</v>
       </c>
       <c r="D22" s="94" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E22" s="47">
         <v>3.5900000000000001E-2</v>
@@ -3135,7 +3094,7 @@
       </c>
       <c r="K22" s="24">
         <f t="shared" si="2"/>
-        <v>3792.9068000000002</v>
+        <v>0</v>
       </c>
       <c r="L22" s="25">
         <f t="shared" si="3"/>
@@ -3147,7 +3106,7 @@
       </c>
       <c r="N22" s="25">
         <f t="shared" si="5"/>
-        <v>136148.952487</v>
+        <v>132356.04568700001</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="15" customHeight="1">
@@ -3161,7 +3120,7 @@
         <v>32</v>
       </c>
       <c r="D23" s="95" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E23" s="48">
         <v>4.1399999999999999E-2</v>
@@ -3187,7 +3146,7 @@
       </c>
       <c r="K23" s="24">
         <f t="shared" si="2"/>
-        <v>4373.9928</v>
+        <v>0</v>
       </c>
       <c r="L23" s="25">
         <f t="shared" si="3"/>
@@ -3199,7 +3158,7 @@
       </c>
       <c r="N23" s="25">
         <f t="shared" si="5"/>
-        <v>157007.42710199999</v>
+        <v>152633.43430199998</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="15" customHeight="1">
@@ -3237,7 +3196,7 @@
       </c>
       <c r="K24" s="24">
         <f t="shared" si="2"/>
-        <v>5652.3819999999996</v>
+        <v>0</v>
       </c>
       <c r="L24" s="25">
         <f t="shared" si="3"/>
@@ -3249,7 +3208,7 @@
       </c>
       <c r="N24" s="25">
         <f t="shared" si="5"/>
-        <v>202896.07125499999</v>
+        <v>197243.68925499998</v>
       </c>
     </row>
     <row r="25" spans="1:15" s="1" customFormat="1" ht="15.75" customHeight="1">
@@ -3260,10 +3219,10 @@
         <v>56</v>
       </c>
       <c r="C25" s="96" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D25" s="96" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E25" s="49">
         <v>3.85E-2</v>
@@ -3289,7 +3248,7 @@
       </c>
       <c r="K25" s="24">
         <f t="shared" si="2"/>
-        <v>4067.6019999999999</v>
+        <v>0</v>
       </c>
       <c r="L25" s="25">
         <f t="shared" si="3"/>
@@ -3301,7 +3260,7 @@
       </c>
       <c r="N25" s="25">
         <f t="shared" si="5"/>
-        <v>146009.32230499998</v>
+        <v>141941.720305</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="15" customHeight="1">
@@ -3339,7 +3298,7 @@
       </c>
       <c r="K26" s="24">
         <f t="shared" si="2"/>
-        <v>3792.9068000000002</v>
+        <v>0</v>
       </c>
       <c r="L26" s="25">
         <f t="shared" si="3"/>
@@ -3351,7 +3310,7 @@
       </c>
       <c r="N26" s="25">
         <f t="shared" si="5"/>
-        <v>136148.952487</v>
+        <v>132356.04568700001</v>
       </c>
     </row>
     <row r="27" spans="1:15" ht="15" customHeight="1">
@@ -3365,24 +3324,24 @@
         <v>35</v>
       </c>
       <c r="D27" s="149" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E27" s="150">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F27" s="151">
-        <v>2287408.8640416628</v>
+        <v>2366233.714203204</v>
       </c>
       <c r="G27" s="161">
-        <v>157007.43</v>
-      </c>
-      <c r="H27" s="182">
+        <v>157010</v>
+      </c>
+      <c r="H27" s="181">
         <f t="shared" si="0"/>
-        <v>2130401.4340416626</v>
+        <v>2209223.714203204</v>
       </c>
       <c r="I27" s="152">
         <f t="shared" si="6"/>
-        <v>78824.853059541521</v>
+        <v>81741.277425518565</v>
       </c>
       <c r="J27" s="152">
         <f t="shared" si="1"/>
@@ -3390,7 +3349,7 @@
       </c>
       <c r="K27" s="152">
         <f t="shared" si="2"/>
-        <v>4373.9928</v>
+        <v>0</v>
       </c>
       <c r="L27" s="153">
         <f t="shared" si="3"/>
@@ -3402,7 +3361,7 @@
       </c>
       <c r="N27" s="153">
         <f t="shared" si="5"/>
-        <v>2366233.714203204</v>
+        <v>2443598.4259307226</v>
       </c>
     </row>
     <row r="28" spans="1:15" ht="17.25" customHeight="1">
@@ -3420,22 +3379,22 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F28" s="17">
-        <v>197243.68925499998</v>
+        <v>197237.37850999995</v>
       </c>
       <c r="G28" s="160">
-        <v>197250</v>
+        <v>190250</v>
       </c>
       <c r="H28" s="68">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6987.3785099999513</v>
       </c>
       <c r="I28" s="24">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>258.53300486999825</v>
       </c>
       <c r="J28" s="24">
         <f t="shared" si="1"/>
-        <v>6.3107450000243261</v>
+        <v>0</v>
       </c>
       <c r="K28" s="24"/>
       <c r="L28" s="25">
@@ -3448,7 +3407,7 @@
       </c>
       <c r="N28" s="25">
         <f t="shared" si="5"/>
-        <v>197237.37850999995</v>
+        <v>204489.60076986992</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="15" customHeight="1">
@@ -3459,7 +3418,7 @@
         <v>60</v>
       </c>
       <c r="C29" s="96" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D29" s="96"/>
       <c r="E29" s="49">
@@ -3486,7 +3445,7 @@
       </c>
       <c r="K29" s="24">
         <f t="shared" si="2"/>
-        <v>4067.6019999999999</v>
+        <v>0</v>
       </c>
       <c r="L29" s="25">
         <f t="shared" si="3"/>
@@ -3498,7 +3457,7 @@
       </c>
       <c r="N29" s="25">
         <f t="shared" si="5"/>
-        <v>146009.32230499998</v>
+        <v>141941.720305</v>
       </c>
       <c r="O29" s="7"/>
     </row>
@@ -3510,19 +3469,20 @@
         <v>61</v>
       </c>
       <c r="C30" s="96" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D30" s="96" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E30" s="49">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F30" s="17">
-        <v>136148.952487</v>
+        <v>136097.904974</v>
       </c>
       <c r="G30" s="160">
-        <v>136200</v>
+        <f>F30</f>
+        <v>136097.904974</v>
       </c>
       <c r="H30" s="24">
         <f t="shared" si="0"/>
@@ -3534,11 +3494,11 @@
       </c>
       <c r="J30" s="24">
         <f t="shared" si="1"/>
-        <v>51.047512999997707</v>
+        <v>0</v>
       </c>
       <c r="K30" s="24">
         <f t="shared" si="2"/>
-        <v>3792.9068000000002</v>
+        <v>0</v>
       </c>
       <c r="L30" s="25">
         <f t="shared" si="3"/>
@@ -3550,7 +3510,7 @@
       </c>
       <c r="N30" s="25">
         <f t="shared" si="5"/>
-        <v>136097.904974</v>
+        <v>132356.04568700001</v>
       </c>
     </row>
     <row r="31" spans="1:15" ht="15" customHeight="1">
@@ -3588,7 +3548,7 @@
       </c>
       <c r="K31" s="24">
         <f t="shared" si="2"/>
-        <v>4373.9928</v>
+        <v>0</v>
       </c>
       <c r="L31" s="25">
         <f t="shared" si="3"/>
@@ -3600,7 +3560,7 @@
       </c>
       <c r="N31" s="25">
         <f t="shared" si="5"/>
-        <v>157007.42710199999</v>
+        <v>152633.43430199998</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="15.75">
@@ -3617,27 +3577,27 @@
       </c>
       <c r="F32" s="100">
         <f>SUM(F9:F31)</f>
-        <v>10008287.113094246</v>
+        <v>9341525.9262949992</v>
       </c>
       <c r="G32" s="100">
         <f>SUM(G9:G31)</f>
-        <v>4651785.9958085511</v>
+        <v>3136024.996325769</v>
       </c>
       <c r="H32" s="126">
         <f>SUM(H9:H31)</f>
-        <v>5357493.540791926</v>
+        <v>6205500.9299692269</v>
       </c>
       <c r="I32" s="54">
         <f>SUM(I9:I31)</f>
-        <v>198227.26100930129</v>
+        <v>229603.53440886142</v>
       </c>
       <c r="J32" s="100">
         <f t="shared" ref="J32" si="8">SUM(J9:J31)</f>
-        <v>992.42350623084349</v>
+        <v>0</v>
       </c>
       <c r="K32" s="91">
         <f>SUM(K9:K31)</f>
-        <v>99999.617999999959</v>
+        <v>0</v>
       </c>
       <c r="L32" s="54">
         <f>SUM(L9:L31)</f>
@@ -3649,7 +3609,7 @@
       </c>
       <c r="N32" s="54">
         <f>SUM(N9:N31)</f>
-        <v>9341525.9262949992</v>
+        <v>10121902.394378088</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="14.25" customHeight="1"/>
@@ -3791,7 +3751,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
       <c r="A1" s="186" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B1" s="187"/>
       <c r="C1" s="187"/>
@@ -3807,7 +3767,7 @@
     <row r="3" spans="1:7">
       <c r="A3" s="57"/>
       <c r="B3" s="59" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G3" s="31"/>
     </row>
@@ -3857,7 +3817,7 @@
         <v>15</v>
       </c>
       <c r="F8" s="75" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G8" s="29" t="s">
         <v>8</v>
@@ -3882,7 +3842,7 @@
       </c>
       <c r="F9" s="71"/>
       <c r="G9" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -3904,7 +3864,7 @@
       </c>
       <c r="F10" s="71"/>
       <c r="G10" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -3926,7 +3886,7 @@
       </c>
       <c r="F11" s="71"/>
       <c r="G11" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -3948,7 +3908,7 @@
       </c>
       <c r="F12" s="71"/>
       <c r="G12" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -3970,7 +3930,7 @@
       </c>
       <c r="F13" s="71"/>
       <c r="G13" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -4018,7 +3978,7 @@
       </c>
       <c r="F15" s="71"/>
       <c r="G15" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -4029,7 +3989,7 @@
         <v>47</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D16" s="45">
         <v>5.3499999999999999E-2</v>
@@ -4040,7 +4000,7 @@
       </c>
       <c r="F16" s="71"/>
       <c r="G16" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -4062,7 +4022,7 @@
       </c>
       <c r="F17" s="71"/>
       <c r="G17" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -4084,7 +4044,7 @@
       </c>
       <c r="F18" s="71"/>
       <c r="G18" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -4132,7 +4092,7 @@
       </c>
       <c r="F20" s="71"/>
       <c r="G20" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -4154,7 +4114,7 @@
       </c>
       <c r="F21" s="71"/>
       <c r="G21" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -4176,7 +4136,7 @@
       </c>
       <c r="F22" s="71"/>
       <c r="G22" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -4198,7 +4158,7 @@
       </c>
       <c r="F23" s="71"/>
       <c r="G23" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="15.75">
@@ -4220,7 +4180,7 @@
       </c>
       <c r="F24" s="71"/>
       <c r="G24" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="15.75">
@@ -4231,7 +4191,7 @@
         <v>56</v>
       </c>
       <c r="C25" s="65" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D25" s="49">
         <v>3.85E-2</v>
@@ -4242,7 +4202,7 @@
       </c>
       <c r="F25" s="71"/>
       <c r="G25" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="15.75">
@@ -4264,7 +4224,7 @@
       </c>
       <c r="F26" s="71"/>
       <c r="G26" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15.75">
@@ -4312,7 +4272,7 @@
       </c>
       <c r="F28" s="71"/>
       <c r="G28" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="15.75">
@@ -4334,7 +4294,7 @@
       </c>
       <c r="F29" s="71"/>
       <c r="G29" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="15.75">
@@ -4356,7 +4316,7 @@
       </c>
       <c r="F30" s="71"/>
       <c r="G30" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="15.75">
@@ -4378,7 +4338,7 @@
       </c>
       <c r="F31" s="71"/>
       <c r="G31" s="71" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="15.75">
@@ -4401,7 +4361,7 @@
     </row>
     <row r="34" spans="3:5" ht="13.5" customHeight="1">
       <c r="C34" s="78" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D34" s="76"/>
       <c r="E34" s="77">
@@ -4421,7 +4381,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -4434,7 +4394,7 @@
     <col min="10" max="10" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="8"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -4444,7 +4404,7 @@
       <c r="G1" s="3"/>
       <c r="H1" s="9"/>
     </row>
-    <row r="2" spans="1:8" ht="48" customHeight="1">
+    <row r="2" spans="1:9" ht="48" customHeight="1">
       <c r="A2" s="10"/>
       <c r="D2" s="221"/>
       <c r="E2" s="222"/>
@@ -4452,7 +4412,7 @@
       <c r="G2" s="222"/>
       <c r="H2" s="223"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" s="10"/>
       <c r="D3" s="14" t="s">
         <v>6</v>
@@ -4464,7 +4424,7 @@
       <c r="G3" s="197"/>
       <c r="H3" s="198"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" s="10"/>
       <c r="D4" s="14" t="s">
         <v>4</v>
@@ -4474,7 +4434,7 @@
       </c>
       <c r="H4" s="11"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" s="10"/>
       <c r="D5" s="14" t="s">
         <v>18</v>
@@ -4484,21 +4444,21 @@
       </c>
       <c r="H5" s="11"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" s="10"/>
       <c r="D6" s="14" t="s">
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H6" s="11"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" s="10"/>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:8" s="5" customFormat="1" ht="18.75">
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="18.75">
       <c r="A8" s="18" t="s">
         <v>5</v>
       </c>
@@ -4509,14 +4469,14 @@
         <v>67</v>
       </c>
       <c r="F8" s="90" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="H8" s="20"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9" s="8"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -4526,7 +4486,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="9"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10" s="15" t="s">
         <v>14</v>
       </c>
@@ -4535,12 +4495,12 @@
       </c>
       <c r="H10" s="11"/>
     </row>
-    <row r="11" spans="1:8" ht="14.25" customHeight="1">
+    <row r="11" spans="1:9" ht="14.25" customHeight="1">
       <c r="A11" s="15"/>
       <c r="E11" s="14"/>
       <c r="H11" s="11"/>
     </row>
-    <row r="12" spans="1:8" ht="67.5" hidden="1" customHeight="1">
+    <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
       <c r="A12" s="229"/>
       <c r="B12" s="190"/>
       <c r="C12" s="190"/>
@@ -4550,7 +4510,7 @@
       <c r="G12" s="190"/>
       <c r="H12" s="230"/>
     </row>
-    <row r="13" spans="1:8" ht="13.5" customHeight="1">
+    <row r="13" spans="1:9" ht="13.5" customHeight="1">
       <c r="A13" s="12"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -4560,9 +4520,9 @@
       <c r="G13" s="4"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:8" ht="15.75">
+    <row r="14" spans="1:9" ht="15.75">
       <c r="A14" s="203" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B14" s="203"/>
       <c r="C14" s="203"/>
@@ -4572,9 +4532,9 @@
       <c r="G14" s="203"/>
       <c r="H14" s="203"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9">
       <c r="A15" s="170" t="s">
-        <v>69</v>
+        <v>151</v>
       </c>
       <c r="B15" s="141"/>
       <c r="C15" s="141"/>
@@ -4583,12 +4543,12 @@
       <c r="F15" s="141"/>
       <c r="G15" s="141"/>
       <c r="H15" s="74">
-        <v>194212.8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>391137.56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="170" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B16" s="141"/>
       <c r="C16" s="141"/>
@@ -4597,12 +4557,13 @@
       <c r="F16" s="141"/>
       <c r="G16" s="141"/>
       <c r="H16" s="74">
-        <v>23811.3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="14.25" customHeight="1">
+        <v>-61604.17</v>
+      </c>
+      <c r="I16" s="7"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="170" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="B17" s="141"/>
       <c r="C17" s="141"/>
@@ -4611,12 +4572,13 @@
       <c r="F17" s="141"/>
       <c r="G17" s="141"/>
       <c r="H17" s="74">
-        <v>33304</v>
-      </c>
+        <v>0.61</v>
+      </c>
+      <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="170" t="s">
-        <v>139</v>
+        <v>75</v>
       </c>
       <c r="B18" s="141"/>
       <c r="C18" s="141"/>
@@ -4625,27 +4587,26 @@
       <c r="F18" s="141"/>
       <c r="G18" s="141"/>
       <c r="H18" s="74">
-        <v>6666.67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="170" t="s">
-        <v>91</v>
-      </c>
-      <c r="B19" s="141"/>
-      <c r="C19" s="141"/>
-      <c r="D19" s="141"/>
-      <c r="E19" s="141"/>
-      <c r="F19" s="141"/>
-      <c r="G19" s="141"/>
-      <c r="H19" s="74">
-        <v>-40634.18</v>
-      </c>
-      <c r="I19" s="7"/>
-    </row>
-    <row r="20" spans="1:9">
+        <f>SUM(H15:H17)</f>
+        <v>329534</v>
+      </c>
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" spans="1:9" ht="0.75" customHeight="1">
+      <c r="A19" s="225" t="s">
+        <v>132</v>
+      </c>
+      <c r="B19" s="225"/>
+      <c r="C19" s="225"/>
+      <c r="D19" s="225"/>
+      <c r="E19" s="225"/>
+      <c r="F19" s="225"/>
+      <c r="G19" s="225"/>
+      <c r="H19" s="225"/>
+    </row>
+    <row r="20" spans="1:9" hidden="1">
       <c r="A20" s="170" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B20" s="141"/>
       <c r="C20" s="141"/>
@@ -4653,15 +4614,10 @@
       <c r="E20" s="141"/>
       <c r="F20" s="141"/>
       <c r="G20" s="141"/>
-      <c r="H20" s="74">
-        <v>0.41</v>
-      </c>
-      <c r="I20" s="7"/>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="170" t="s">
-        <v>77</v>
-      </c>
+      <c r="H20" s="74"/>
+    </row>
+    <row r="21" spans="1:9" hidden="1">
+      <c r="A21" s="170"/>
       <c r="B21" s="141"/>
       <c r="C21" s="141"/>
       <c r="D21" s="141"/>
@@ -4669,86 +4625,87 @@
       <c r="F21" s="141"/>
       <c r="G21" s="141"/>
       <c r="H21" s="74">
-        <f>SUM(H15:H20)</f>
-        <v>217361</v>
-      </c>
-      <c r="I21" s="7"/>
-    </row>
-    <row r="22" spans="1:9" ht="0.75" customHeight="1">
-      <c r="A22" s="225" t="s">
-        <v>136</v>
-      </c>
-      <c r="B22" s="225"/>
-      <c r="C22" s="225"/>
-      <c r="D22" s="225"/>
-      <c r="E22" s="225"/>
-      <c r="F22" s="225"/>
-      <c r="G22" s="225"/>
-      <c r="H22" s="225"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" hidden="1">
+      <c r="A22" s="170"/>
+      <c r="B22" s="141"/>
+      <c r="C22" s="141"/>
+      <c r="D22" s="141"/>
+      <c r="E22" s="141"/>
+      <c r="F22" s="141"/>
+      <c r="G22" s="141"/>
+      <c r="H22" s="74">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:9" hidden="1">
-      <c r="A23" s="170" t="s">
-        <v>136</v>
-      </c>
+      <c r="A23" s="170"/>
       <c r="B23" s="141"/>
       <c r="C23" s="141"/>
       <c r="D23" s="141"/>
       <c r="E23" s="141"/>
       <c r="F23" s="141"/>
       <c r="G23" s="141"/>
-      <c r="H23" s="74"/>
+      <c r="H23" s="74">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:9" hidden="1">
-      <c r="A24" s="170"/>
+      <c r="A24" s="170" t="s">
+        <v>133</v>
+      </c>
       <c r="B24" s="141"/>
       <c r="C24" s="141"/>
       <c r="D24" s="141"/>
       <c r="E24" s="141"/>
       <c r="F24" s="141"/>
       <c r="G24" s="141"/>
-      <c r="H24" s="74">
-        <v>0</v>
-      </c>
+      <c r="H24" s="74"/>
     </row>
     <row r="25" spans="1:9" hidden="1">
-      <c r="A25" s="170"/>
+      <c r="A25" s="170" t="s">
+        <v>89</v>
+      </c>
       <c r="B25" s="141"/>
       <c r="C25" s="141"/>
       <c r="D25" s="141"/>
       <c r="E25" s="141"/>
       <c r="F25" s="141"/>
       <c r="G25" s="141"/>
-      <c r="H25" s="74">
-        <v>0</v>
-      </c>
+      <c r="H25" s="74"/>
     </row>
     <row r="26" spans="1:9" hidden="1">
-      <c r="A26" s="170"/>
+      <c r="A26" s="170" t="s">
+        <v>75</v>
+      </c>
       <c r="B26" s="141"/>
       <c r="C26" s="141"/>
       <c r="D26" s="141"/>
       <c r="E26" s="141"/>
       <c r="F26" s="141"/>
       <c r="G26" s="141"/>
-      <c r="H26" s="74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" hidden="1">
-      <c r="A27" s="170" t="s">
-        <v>137</v>
-      </c>
-      <c r="B27" s="141"/>
-      <c r="C27" s="141"/>
-      <c r="D27" s="141"/>
-      <c r="E27" s="141"/>
-      <c r="F27" s="141"/>
-      <c r="G27" s="141"/>
-      <c r="H27" s="74"/>
-    </row>
-    <row r="28" spans="1:9" hidden="1">
-      <c r="A28" s="170" t="s">
-        <v>91</v>
+      <c r="H26" s="70">
+        <f>SUM(H20:H25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="224" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27" s="224"/>
+      <c r="C27" s="224"/>
+      <c r="D27" s="224"/>
+      <c r="E27" s="224"/>
+      <c r="F27" s="224"/>
+      <c r="G27" s="224"/>
+      <c r="H27" s="224"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="141" t="s">
+        <v>145</v>
       </c>
       <c r="B28" s="141"/>
       <c r="C28" s="141"/>
@@ -4756,51 +4713,49 @@
       <c r="E28" s="141"/>
       <c r="F28" s="141"/>
       <c r="G28" s="141"/>
-      <c r="H28" s="74"/>
-    </row>
-    <row r="29" spans="1:9" hidden="1">
-      <c r="A29" s="170" t="s">
-        <v>77</v>
-      </c>
+      <c r="H28" s="74">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="141"/>
       <c r="B29" s="141"/>
       <c r="C29" s="141"/>
       <c r="D29" s="141"/>
       <c r="E29" s="141"/>
       <c r="F29" s="141"/>
       <c r="G29" s="141"/>
-      <c r="H29" s="70">
-        <f>SUM(H23:H28)</f>
-        <v>0</v>
-      </c>
+      <c r="H29" s="74"/>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="224" t="s">
-        <v>141</v>
-      </c>
-      <c r="B30" s="224"/>
-      <c r="C30" s="224"/>
-      <c r="D30" s="224"/>
-      <c r="E30" s="224"/>
-      <c r="F30" s="224"/>
-      <c r="G30" s="224"/>
-      <c r="H30" s="224"/>
-    </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="141" t="s">
-        <v>152</v>
-      </c>
-      <c r="B31" s="141"/>
-      <c r="C31" s="141"/>
-      <c r="D31" s="141"/>
-      <c r="E31" s="141"/>
-      <c r="F31" s="141"/>
-      <c r="G31" s="141"/>
-      <c r="H31" s="74">
+      <c r="A30" s="141" t="s">
+        <v>75</v>
+      </c>
+      <c r="B30" s="141"/>
+      <c r="C30" s="141"/>
+      <c r="D30" s="141"/>
+      <c r="E30" s="141"/>
+      <c r="F30" s="141"/>
+      <c r="G30" s="141"/>
+      <c r="H30" s="74">
+        <f>SUM(H28:H29)</f>
         <v>32000</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="141"/>
+    <row r="31" spans="1:9" ht="14.25" customHeight="1">
+      <c r="A31" s="204" t="s">
+        <v>90</v>
+      </c>
+      <c r="B31" s="204"/>
+      <c r="C31" s="204"/>
+      <c r="D31" s="204"/>
+      <c r="E31" s="204"/>
+      <c r="F31" s="204"/>
+      <c r="G31" s="204"/>
+      <c r="H31" s="204"/>
+    </row>
+    <row r="32" spans="1:9" hidden="1">
+      <c r="A32" s="170"/>
       <c r="B32" s="141"/>
       <c r="C32" s="141"/>
       <c r="D32" s="141"/>
@@ -4810,60 +4765,64 @@
       <c r="H32" s="74"/>
     </row>
     <row r="33" spans="1:8">
-      <c r="A33" s="141" t="s">
-        <v>77</v>
-      </c>
-      <c r="B33" s="141"/>
+      <c r="A33" s="170" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="171"/>
       <c r="C33" s="141"/>
       <c r="D33" s="141"/>
       <c r="E33" s="141"/>
       <c r="F33" s="141"/>
       <c r="G33" s="141"/>
       <c r="H33" s="74">
-        <f>SUM(H31:H32)</f>
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A34" s="204" t="s">
-        <v>94</v>
-      </c>
-      <c r="B34" s="204"/>
-      <c r="C34" s="204"/>
-      <c r="D34" s="204"/>
-      <c r="E34" s="204"/>
-      <c r="F34" s="204"/>
-      <c r="G34" s="204"/>
-      <c r="H34" s="204"/>
-    </row>
-    <row r="35" spans="1:8" hidden="1">
-      <c r="A35" s="170"/>
+        <f>11996.77+1332.97+29278.65</f>
+        <v>42608.39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="141" t="s">
+        <v>152</v>
+      </c>
+      <c r="B34" s="141"/>
+      <c r="C34" s="141"/>
+      <c r="D34" s="141"/>
+      <c r="E34" s="141"/>
+      <c r="F34" s="141"/>
+      <c r="G34" s="141"/>
+      <c r="H34" s="74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="141" t="s">
+        <v>74</v>
+      </c>
       <c r="B35" s="141"/>
       <c r="C35" s="141"/>
       <c r="D35" s="141"/>
       <c r="E35" s="141"/>
       <c r="F35" s="141"/>
       <c r="G35" s="141"/>
-      <c r="H35" s="74"/>
+      <c r="H35" s="74">
+        <f>SUM(H32:H34)</f>
+        <v>42608.39</v>
+      </c>
     </row>
     <row r="36" spans="1:8">
-      <c r="A36" s="170" t="s">
-        <v>84</v>
-      </c>
-      <c r="B36" s="171"/>
-      <c r="C36" s="141"/>
-      <c r="D36" s="141"/>
-      <c r="E36" s="141"/>
-      <c r="F36" s="141"/>
-      <c r="G36" s="141"/>
-      <c r="H36" s="231">
-        <f>11996.77+1332.97+29278.65</f>
-        <v>42608.39</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+      <c r="A36" s="204" t="s">
+        <v>137</v>
+      </c>
+      <c r="B36" s="204"/>
+      <c r="C36" s="204"/>
+      <c r="D36" s="204"/>
+      <c r="E36" s="204"/>
+      <c r="F36" s="204"/>
+      <c r="G36" s="204"/>
+      <c r="H36" s="204"/>
+    </row>
+    <row r="37" spans="1:8" ht="14.25" customHeight="1">
       <c r="A37" s="141" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="B37" s="141"/>
       <c r="C37" s="141"/>
@@ -4872,12 +4831,12 @@
       <c r="F37" s="141"/>
       <c r="G37" s="141"/>
       <c r="H37" s="74">
-        <v>0</v>
+        <v>936177.69</v>
       </c>
     </row>
     <row r="38" spans="1:8">
-      <c r="A38" s="141" t="s">
-        <v>76</v>
+      <c r="A38" s="172" t="s">
+        <v>102</v>
       </c>
       <c r="B38" s="141"/>
       <c r="C38" s="141"/>
@@ -4886,39 +4845,39 @@
       <c r="F38" s="141"/>
       <c r="G38" s="141"/>
       <c r="H38" s="74">
-        <f>SUM(H35:H37)</f>
-        <v>42608.39</v>
+        <v>74572.05</v>
       </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="204" t="s">
-        <v>142</v>
-      </c>
-      <c r="B39" s="204"/>
-      <c r="C39" s="204"/>
-      <c r="D39" s="204"/>
-      <c r="E39" s="204"/>
-      <c r="F39" s="204"/>
-      <c r="G39" s="204"/>
-      <c r="H39" s="204"/>
-    </row>
-    <row r="40" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A40" s="141" t="s">
-        <v>161</v>
-      </c>
-      <c r="B40" s="141"/>
-      <c r="C40" s="141"/>
-      <c r="D40" s="141"/>
-      <c r="E40" s="141"/>
-      <c r="F40" s="141"/>
-      <c r="G40" s="141"/>
-      <c r="H40" s="231">
-        <v>936177.69</v>
-      </c>
+      <c r="A39" s="141" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="141"/>
+      <c r="C39" s="141"/>
+      <c r="D39" s="141"/>
+      <c r="E39" s="141"/>
+      <c r="F39" s="141"/>
+      <c r="G39" s="141"/>
+      <c r="H39" s="145">
+        <f>SUM(H37:H38)</f>
+        <v>1010749.74</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="203" t="s">
+        <v>138</v>
+      </c>
+      <c r="B40" s="203"/>
+      <c r="C40" s="203"/>
+      <c r="D40" s="203"/>
+      <c r="E40" s="203"/>
+      <c r="F40" s="203"/>
+      <c r="G40" s="203"/>
+      <c r="H40" s="203"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="172" t="s">
-        <v>106</v>
+      <c r="A41" s="81" t="s">
+        <v>69</v>
       </c>
       <c r="B41" s="141"/>
       <c r="C41" s="141"/>
@@ -4926,13 +4885,13 @@
       <c r="E41" s="141"/>
       <c r="F41" s="141"/>
       <c r="G41" s="141"/>
-      <c r="H41" s="231">
-        <v>75572.05</v>
+      <c r="H41" s="74">
+        <v>47700</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="141" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B42" s="141"/>
       <c r="C42" s="141"/>
@@ -4940,26 +4899,27 @@
       <c r="E42" s="141"/>
       <c r="F42" s="141"/>
       <c r="G42" s="141"/>
-      <c r="H42" s="145">
-        <f>SUM(H40:H41)</f>
-        <v>1011749.74</v>
+      <c r="H42" s="74">
+        <v>19099.96</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="A43" s="203" t="s">
-        <v>143</v>
-      </c>
-      <c r="B43" s="203"/>
-      <c r="C43" s="203"/>
-      <c r="D43" s="203"/>
-      <c r="E43" s="203"/>
-      <c r="F43" s="203"/>
-      <c r="G43" s="203"/>
-      <c r="H43" s="203"/>
+      <c r="A43" s="141" t="s">
+        <v>148</v>
+      </c>
+      <c r="B43" s="141"/>
+      <c r="C43" s="141"/>
+      <c r="D43" s="141"/>
+      <c r="E43" s="141"/>
+      <c r="F43" s="141"/>
+      <c r="G43" s="141"/>
+      <c r="H43" s="74">
+        <v>55000</v>
+      </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="A44" s="81" t="s">
-        <v>71</v>
+      <c r="A44" s="141" t="s">
+        <v>153</v>
       </c>
       <c r="B44" s="141"/>
       <c r="C44" s="141"/>
@@ -4968,40 +4928,37 @@
       <c r="F44" s="141"/>
       <c r="G44" s="141"/>
       <c r="H44" s="74">
-        <v>47700</v>
+        <v>131648</v>
       </c>
     </row>
     <row r="45" spans="1:8">
-      <c r="A45" s="141" t="s">
-        <v>72</v>
-      </c>
+      <c r="A45" s="141"/>
       <c r="B45" s="141"/>
       <c r="C45" s="141"/>
       <c r="D45" s="141"/>
       <c r="E45" s="141"/>
       <c r="F45" s="141"/>
       <c r="G45" s="141"/>
-      <c r="H45" s="231">
-        <v>19099.96</v>
+      <c r="H45" s="70">
+        <f>SUM(H41:H44)</f>
+        <v>253447.96</v>
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="A46" s="141" t="s">
-        <v>154</v>
-      </c>
-      <c r="B46" s="141"/>
-      <c r="C46" s="141"/>
-      <c r="D46" s="141"/>
-      <c r="E46" s="141"/>
-      <c r="F46" s="141"/>
-      <c r="G46" s="141"/>
-      <c r="H46" s="74">
-        <v>180000</v>
-      </c>
+      <c r="A46" s="203" t="s">
+        <v>139</v>
+      </c>
+      <c r="B46" s="203"/>
+      <c r="C46" s="203"/>
+      <c r="D46" s="203"/>
+      <c r="E46" s="203"/>
+      <c r="F46" s="203"/>
+      <c r="G46" s="203"/>
+      <c r="H46" s="203"/>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="141" t="s">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c r="B47" s="141"/>
       <c r="C47" s="141"/>
@@ -5010,12 +4967,12 @@
       <c r="F47" s="141"/>
       <c r="G47" s="141"/>
       <c r="H47" s="74">
-        <v>55000</v>
+        <v>139785.35999999999</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="141" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="B48" s="141"/>
       <c r="C48" s="141"/>
@@ -5024,26 +4981,22 @@
       <c r="F48" s="141"/>
       <c r="G48" s="141"/>
       <c r="H48" s="74">
-        <v>165000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="141" t="s">
-        <v>160</v>
-      </c>
+      <c r="A49" s="141"/>
       <c r="B49" s="141"/>
       <c r="C49" s="141"/>
       <c r="D49" s="141"/>
       <c r="E49" s="141"/>
       <c r="F49" s="141"/>
       <c r="G49" s="141"/>
-      <c r="H49" s="231">
-        <v>131648</v>
-      </c>
+      <c r="H49" s="74"/>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="141" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B50" s="141"/>
       <c r="C50" s="141"/>
@@ -5051,107 +5004,101 @@
       <c r="E50" s="141"/>
       <c r="F50" s="141"/>
       <c r="G50" s="141"/>
-      <c r="H50" s="70">
-        <f>SUM(H44:H49)</f>
-        <v>598447.96</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
-      <c r="A51" s="203" t="s">
-        <v>144</v>
-      </c>
-      <c r="B51" s="203"/>
-      <c r="C51" s="203"/>
-      <c r="D51" s="203"/>
-      <c r="E51" s="203"/>
-      <c r="F51" s="203"/>
-      <c r="G51" s="203"/>
-      <c r="H51" s="203"/>
-    </row>
-    <row r="52" spans="1:11">
-      <c r="A52" s="141" t="s">
-        <v>73</v>
-      </c>
-      <c r="B52" s="141"/>
-      <c r="C52" s="141"/>
-      <c r="D52" s="141"/>
-      <c r="E52" s="141"/>
-      <c r="F52" s="141"/>
-      <c r="G52" s="141"/>
-      <c r="H52" s="233">
-        <v>139785.35999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
-      <c r="A53" s="141" t="s">
-        <v>125</v>
-      </c>
-      <c r="B53" s="141"/>
-      <c r="C53" s="141"/>
-      <c r="D53" s="141"/>
-      <c r="E53" s="141"/>
-      <c r="F53" s="141"/>
-      <c r="G53" s="141"/>
-      <c r="H53" s="233">
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
-      <c r="A54" s="141"/>
-      <c r="B54" s="141"/>
-      <c r="C54" s="141"/>
-      <c r="D54" s="141"/>
-      <c r="E54" s="141"/>
-      <c r="F54" s="141"/>
-      <c r="G54" s="141"/>
-      <c r="H54" s="74"/>
-    </row>
-    <row r="55" spans="1:11">
-      <c r="A55" s="141" t="s">
-        <v>76</v>
-      </c>
-      <c r="B55" s="141"/>
-      <c r="C55" s="141"/>
-      <c r="D55" s="141"/>
-      <c r="E55" s="141"/>
-      <c r="F55" s="141"/>
-      <c r="G55" s="141"/>
-      <c r="H55" s="173">
-        <f>SUM(H52:H54)</f>
+      <c r="H50" s="173">
+        <f>SUM(H47:H49)</f>
         <v>167785.36</v>
       </c>
-      <c r="K55" s="7"/>
+      <c r="K50" s="7"/>
+    </row>
+    <row r="51" spans="1:11" s="6" customFormat="1">
+      <c r="A51" s="205" t="s">
+        <v>140</v>
+      </c>
+      <c r="B51" s="206"/>
+      <c r="C51" s="206"/>
+      <c r="D51" s="206"/>
+      <c r="E51" s="206"/>
+      <c r="F51" s="206"/>
+      <c r="G51" s="206"/>
+      <c r="H51" s="207"/>
+    </row>
+    <row r="52" spans="1:11" s="6" customFormat="1">
+      <c r="A52" s="81" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" s="81"/>
+      <c r="C52" s="81"/>
+      <c r="D52" s="81"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
+      <c r="H52" s="70">
+        <v>23006</v>
+      </c>
+      <c r="I52" s="60"/>
+    </row>
+    <row r="53" spans="1:11" s="6" customFormat="1">
+      <c r="A53" s="81" t="s">
+        <v>75</v>
+      </c>
+      <c r="B53" s="81"/>
+      <c r="C53" s="81"/>
+      <c r="D53" s="81"/>
+      <c r="E53" s="81"/>
+      <c r="F53" s="81"/>
+      <c r="G53" s="81"/>
+      <c r="H53" s="70">
+        <f>SUM(H52)</f>
+        <v>23006</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" s="6" customFormat="1">
+      <c r="A54" s="203" t="s">
+        <v>141</v>
+      </c>
+      <c r="B54" s="203"/>
+      <c r="C54" s="203"/>
+      <c r="D54" s="203"/>
+      <c r="E54" s="203"/>
+      <c r="F54" s="203"/>
+      <c r="G54" s="203"/>
+      <c r="H54" s="203"/>
+    </row>
+    <row r="55" spans="1:11" s="6" customFormat="1">
+      <c r="A55" s="81"/>
+      <c r="B55" s="81"/>
+      <c r="C55" s="81"/>
+      <c r="D55" s="81"/>
+      <c r="E55" s="81"/>
+      <c r="F55" s="81"/>
+      <c r="G55" s="81"/>
+      <c r="H55" s="70"/>
     </row>
     <row r="56" spans="1:11" s="6" customFormat="1">
-      <c r="A56" s="205" t="s">
-        <v>145</v>
-      </c>
-      <c r="B56" s="206"/>
-      <c r="C56" s="206"/>
-      <c r="D56" s="206"/>
-      <c r="E56" s="206"/>
-      <c r="F56" s="206"/>
-      <c r="G56" s="206"/>
-      <c r="H56" s="207"/>
+      <c r="A56" s="81"/>
+      <c r="B56" s="81"/>
+      <c r="C56" s="81"/>
+      <c r="D56" s="81"/>
+      <c r="E56" s="81"/>
+      <c r="F56" s="81"/>
+      <c r="G56" s="81"/>
+      <c r="H56" s="70"/>
     </row>
     <row r="57" spans="1:11" s="6" customFormat="1">
-      <c r="A57" s="81" t="s">
-        <v>127</v>
-      </c>
+      <c r="A57" s="81"/>
       <c r="B57" s="81"/>
       <c r="C57" s="81"/>
       <c r="D57" s="81"/>
       <c r="E57" s="81"/>
       <c r="F57" s="81"/>
       <c r="G57" s="81"/>
-      <c r="H57" s="232">
-        <v>20546.41</v>
-      </c>
-      <c r="I57" s="60"/>
-    </row>
-    <row r="58" spans="1:11" s="6" customFormat="1">
+      <c r="H57" s="70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" s="6" customFormat="1" ht="21" customHeight="1">
       <c r="A58" s="81" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B58" s="81"/>
       <c r="C58" s="81"/>
@@ -5160,653 +5107,586 @@
       <c r="F58" s="81"/>
       <c r="G58" s="81"/>
       <c r="H58" s="70">
-        <f>SUM(H57)</f>
-        <v>20546.41</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" s="6" customFormat="1">
-      <c r="A59" s="203" t="s">
-        <v>146</v>
-      </c>
-      <c r="B59" s="203"/>
-      <c r="C59" s="203"/>
-      <c r="D59" s="203"/>
-      <c r="E59" s="203"/>
-      <c r="F59" s="203"/>
-      <c r="G59" s="203"/>
-      <c r="H59" s="203"/>
-    </row>
-    <row r="60" spans="1:11" s="6" customFormat="1">
-      <c r="A60" s="81" t="s">
-        <v>150</v>
-      </c>
-      <c r="B60" s="81"/>
-      <c r="C60" s="81"/>
-      <c r="D60" s="81"/>
-      <c r="E60" s="81"/>
-      <c r="F60" s="81"/>
-      <c r="G60" s="81"/>
-      <c r="H60" s="70">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" s="6" customFormat="1">
-      <c r="A61" s="81"/>
-      <c r="B61" s="81"/>
-      <c r="C61" s="81"/>
-      <c r="D61" s="81"/>
-      <c r="E61" s="81"/>
-      <c r="F61" s="81"/>
-      <c r="G61" s="81"/>
-      <c r="H61" s="70"/>
-    </row>
-    <row r="62" spans="1:11" s="6" customFormat="1">
-      <c r="A62" s="81"/>
-      <c r="B62" s="81"/>
-      <c r="C62" s="81"/>
-      <c r="D62" s="81"/>
-      <c r="E62" s="81"/>
-      <c r="F62" s="81"/>
-      <c r="G62" s="81"/>
-      <c r="H62" s="70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A63" s="81" t="s">
-        <v>78</v>
-      </c>
-      <c r="B63" s="81"/>
-      <c r="C63" s="81"/>
-      <c r="D63" s="81"/>
-      <c r="E63" s="81"/>
-      <c r="F63" s="81"/>
-      <c r="G63" s="81"/>
-      <c r="H63" s="70">
-        <f>SUM(H60:H62)</f>
-        <v>100000</v>
-      </c>
-      <c r="I63" s="60"/>
+        <f>SUM(H55:H57)</f>
+        <v>0</v>
+      </c>
+      <c r="I58" s="60"/>
+    </row>
+    <row r="59" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A59" s="205"/>
+      <c r="B59" s="206"/>
+      <c r="C59" s="206"/>
+      <c r="D59" s="206"/>
+      <c r="E59" s="206"/>
+      <c r="F59" s="206"/>
+      <c r="G59" s="206"/>
+      <c r="H59" s="207"/>
+    </row>
+    <row r="60" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
+      <c r="A60" s="82"/>
+      <c r="B60" s="83"/>
+      <c r="C60" s="83"/>
+      <c r="D60" s="83"/>
+      <c r="E60" s="83"/>
+      <c r="F60" s="83"/>
+      <c r="G60" s="83"/>
+      <c r="H60" s="162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
+      <c r="A61" s="163"/>
+      <c r="B61" s="164"/>
+      <c r="C61" s="164"/>
+      <c r="D61" s="164"/>
+      <c r="E61" s="164"/>
+      <c r="F61" s="164"/>
+      <c r="G61" s="164"/>
+      <c r="H61" s="165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A62" s="166"/>
+      <c r="B62" s="167"/>
+      <c r="C62" s="167"/>
+      <c r="D62" s="167"/>
+      <c r="E62" s="167"/>
+      <c r="F62" s="167"/>
+      <c r="G62" s="167"/>
+      <c r="H62" s="162">
+        <f>H60+H61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A63" s="216" t="s">
+        <v>84</v>
+      </c>
+      <c r="B63" s="217"/>
+      <c r="C63" s="217"/>
+      <c r="D63" s="217"/>
+      <c r="E63" s="217"/>
+      <c r="F63" s="217"/>
+      <c r="G63" s="217"/>
+      <c r="H63" s="168">
+        <f>H58</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="64" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A64" s="205"/>
-      <c r="B64" s="206"/>
-      <c r="C64" s="206"/>
-      <c r="D64" s="206"/>
-      <c r="E64" s="206"/>
-      <c r="F64" s="206"/>
-      <c r="G64" s="206"/>
-      <c r="H64" s="207"/>
-    </row>
-    <row r="65" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
-      <c r="A65" s="82"/>
-      <c r="B65" s="83"/>
-      <c r="C65" s="83"/>
-      <c r="D65" s="83"/>
-      <c r="E65" s="83"/>
-      <c r="F65" s="83"/>
-      <c r="G65" s="83"/>
-      <c r="H65" s="162">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
-      <c r="A66" s="163"/>
-      <c r="B66" s="164"/>
-      <c r="C66" s="164"/>
-      <c r="D66" s="164"/>
-      <c r="E66" s="164"/>
-      <c r="F66" s="164"/>
-      <c r="G66" s="164"/>
-      <c r="H66" s="165">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A67" s="166"/>
-      <c r="B67" s="167"/>
-      <c r="C67" s="167"/>
-      <c r="D67" s="167"/>
-      <c r="E67" s="167"/>
-      <c r="F67" s="167"/>
-      <c r="G67" s="167"/>
-      <c r="H67" s="162">
-        <f>H65+H66</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A68" s="216" t="s">
+      <c r="A64" s="219"/>
+      <c r="B64" s="219"/>
+      <c r="C64" s="219"/>
+      <c r="D64" s="219"/>
+      <c r="E64" s="219"/>
+      <c r="F64" s="219"/>
+      <c r="G64" s="219"/>
+      <c r="H64" s="219"/>
+    </row>
+    <row r="65" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
+      <c r="A65" s="220"/>
+      <c r="B65" s="220"/>
+      <c r="C65" s="220"/>
+      <c r="D65" s="220"/>
+      <c r="E65" s="220"/>
+      <c r="F65" s="220"/>
+      <c r="G65" s="220"/>
+      <c r="H65" s="220"/>
+    </row>
+    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A66" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="B68" s="217"/>
-      <c r="C68" s="217"/>
-      <c r="D68" s="217"/>
-      <c r="E68" s="217"/>
-      <c r="F68" s="217"/>
-      <c r="G68" s="217"/>
-      <c r="H68" s="168">
-        <f>H63</f>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A69" s="219"/>
-      <c r="B69" s="219"/>
-      <c r="C69" s="219"/>
-      <c r="D69" s="219"/>
-      <c r="E69" s="219"/>
-      <c r="F69" s="219"/>
-      <c r="G69" s="219"/>
-      <c r="H69" s="219"/>
-    </row>
-    <row r="70" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A70" s="220"/>
-      <c r="B70" s="220"/>
-      <c r="C70" s="220"/>
-      <c r="D70" s="220"/>
-      <c r="E70" s="220"/>
-      <c r="F70" s="220"/>
-      <c r="G70" s="220"/>
-      <c r="H70" s="220"/>
-    </row>
-    <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A71" s="218" t="s">
+      <c r="B66" s="218"/>
+      <c r="C66" s="218"/>
+      <c r="D66" s="218"/>
+      <c r="E66" s="218"/>
+      <c r="F66" s="218"/>
+      <c r="G66" s="218"/>
+      <c r="H66" s="169"/>
+    </row>
+    <row r="67" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A67" s="226"/>
+      <c r="B67" s="227"/>
+      <c r="C67" s="227"/>
+      <c r="D67" s="227"/>
+      <c r="E67" s="227"/>
+      <c r="F67" s="227"/>
+      <c r="G67" s="228"/>
+      <c r="H67" s="74"/>
+    </row>
+    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A68" s="131" t="s">
+        <v>75</v>
+      </c>
+      <c r="B68" s="81"/>
+      <c r="C68" s="81"/>
+      <c r="D68" s="81"/>
+      <c r="E68" s="81"/>
+      <c r="F68" s="81"/>
+      <c r="G68" s="81"/>
+      <c r="H68" s="70">
+        <f>SUM(H67:H67)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A69" s="132"/>
+      <c r="B69" s="132"/>
+      <c r="C69" s="132"/>
+      <c r="D69" s="132"/>
+      <c r="E69" s="132"/>
+      <c r="F69" s="132"/>
+      <c r="G69" s="132"/>
+      <c r="H69" s="133"/>
+    </row>
+    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A70" s="199" t="s">
+        <v>85</v>
+      </c>
+      <c r="B70" s="200"/>
+      <c r="C70" s="200"/>
+      <c r="D70" s="200"/>
+      <c r="E70" s="200"/>
+      <c r="F70" s="200"/>
+      <c r="G70" s="200"/>
+      <c r="H70" s="134">
+        <f>H68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A71" s="211" t="s">
+        <v>91</v>
+      </c>
+      <c r="B71" s="212"/>
+      <c r="C71" s="212"/>
+      <c r="D71" s="212"/>
+      <c r="E71" s="212"/>
+      <c r="F71" s="212"/>
+      <c r="G71" s="213"/>
+      <c r="H71" s="134">
+        <v>27666.48</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A72" s="211" t="s">
+        <v>96</v>
+      </c>
+      <c r="B72" s="212"/>
+      <c r="C72" s="212"/>
+      <c r="D72" s="212"/>
+      <c r="E72" s="212"/>
+      <c r="F72" s="212"/>
+      <c r="G72" s="213"/>
+      <c r="H72" s="134">
+        <v>1800000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="18.75">
+      <c r="A73" s="199" t="s">
+        <v>92</v>
+      </c>
+      <c r="B73" s="200"/>
+      <c r="C73" s="200"/>
+      <c r="D73" s="200"/>
+      <c r="E73" s="200"/>
+      <c r="F73" s="200"/>
+      <c r="G73" s="200"/>
+      <c r="H73" s="134">
+        <f>H30+H39+H45+H50+H53+H35+H18+H26</f>
+        <v>1859131.45</v>
+      </c>
+      <c r="J73" s="7"/>
+      <c r="K73" s="146"/>
+    </row>
+    <row r="74" spans="1:11" ht="18.75">
+      <c r="A74" s="208" t="s">
+        <v>126</v>
+      </c>
+      <c r="B74" s="209"/>
+      <c r="C74" s="209"/>
+      <c r="D74" s="209"/>
+      <c r="E74" s="209"/>
+      <c r="F74" s="209"/>
+      <c r="G74" s="210"/>
+      <c r="H74" s="135">
+        <f>H71+H73</f>
+        <v>1886797.93</v>
+      </c>
+      <c r="I74" s="130"/>
+      <c r="J74" s="189"/>
+      <c r="K74" s="189"/>
+    </row>
+    <row r="75" spans="1:11" ht="18.75">
+      <c r="A75" s="208" t="s">
+        <v>97</v>
+      </c>
+      <c r="B75" s="209"/>
+      <c r="C75" s="209"/>
+      <c r="D75" s="209"/>
+      <c r="E75" s="209"/>
+      <c r="F75" s="209"/>
+      <c r="G75" s="210"/>
+      <c r="H75" s="136">
+        <f>H72+H70</f>
+        <v>1800000</v>
+      </c>
+      <c r="J75" s="146"/>
+    </row>
+    <row r="76" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A76" s="214" t="s">
+        <v>87</v>
+      </c>
+      <c r="B76" s="215"/>
+      <c r="C76" s="215"/>
+      <c r="D76" s="215"/>
+      <c r="E76" s="215"/>
+      <c r="F76" s="215"/>
+      <c r="G76" s="215"/>
+      <c r="H76" s="137">
+        <f>H73+H70</f>
+        <v>1859131.45</v>
+      </c>
+      <c r="J76" s="7"/>
+    </row>
+    <row r="77" spans="1:11" ht="18.75" hidden="1">
+      <c r="A77" s="201" t="s">
+        <v>17</v>
+      </c>
+      <c r="B77" s="202"/>
+      <c r="C77" s="202"/>
+      <c r="D77" s="202"/>
+      <c r="E77" s="202"/>
+      <c r="F77" s="202"/>
+      <c r="G77" s="202"/>
+      <c r="H77" s="138">
+        <f>H62</f>
+        <v>0</v>
+      </c>
+      <c r="J77" s="7"/>
+    </row>
+    <row r="78" spans="1:11" ht="18.75" hidden="1">
+      <c r="A78" s="139"/>
+      <c r="B78" s="139"/>
+      <c r="C78" s="139"/>
+      <c r="D78" s="139"/>
+      <c r="E78" s="139"/>
+      <c r="F78" s="139"/>
+      <c r="G78" s="139"/>
+      <c r="H78" s="140"/>
+      <c r="J78" s="7"/>
+    </row>
+    <row r="79" spans="1:11" ht="18.75" hidden="1">
+      <c r="A79" s="139"/>
+      <c r="B79" s="139"/>
+      <c r="C79" s="139"/>
+      <c r="D79" s="139"/>
+      <c r="E79" s="139"/>
+      <c r="F79" s="139"/>
+      <c r="G79" s="139"/>
+      <c r="H79" s="140"/>
+      <c r="J79" s="7"/>
+    </row>
+    <row r="80" spans="1:11" ht="18.75" hidden="1">
+      <c r="A80" s="139"/>
+      <c r="B80" s="139"/>
+      <c r="C80" s="139"/>
+      <c r="D80" s="139"/>
+      <c r="E80" s="139"/>
+      <c r="F80" s="139"/>
+      <c r="G80" s="139"/>
+      <c r="H80" s="140"/>
+      <c r="J80" s="7"/>
+    </row>
+    <row r="81" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A81" s="141"/>
+      <c r="B81" s="141"/>
+      <c r="C81" s="141"/>
+      <c r="D81" s="141"/>
+      <c r="E81" s="141"/>
+      <c r="F81" s="141"/>
+      <c r="G81" s="141"/>
+      <c r="H81" s="141"/>
+    </row>
+    <row r="82" spans="1:11" ht="18.75">
+      <c r="A82" s="194" t="s">
+        <v>10</v>
+      </c>
+      <c r="B82" s="195"/>
+      <c r="C82" s="195"/>
+      <c r="D82" s="195"/>
+      <c r="E82" s="195"/>
+      <c r="F82" s="195"/>
+      <c r="G82" s="195"/>
+      <c r="H82" s="196"/>
+    </row>
+    <row r="83" spans="1:11" ht="18.75">
+      <c r="A83" s="142" t="s">
+        <v>12</v>
+      </c>
+      <c r="B83" s="143"/>
+      <c r="C83" s="143"/>
+      <c r="D83" s="143"/>
+      <c r="E83" s="143"/>
+      <c r="F83" s="143"/>
+      <c r="G83" s="143"/>
+      <c r="H83" s="144">
+        <v>3155289.5402832869</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" s="82" t="s">
+        <v>135</v>
+      </c>
+      <c r="B84" s="83"/>
+      <c r="C84" s="83"/>
+      <c r="D84" s="83"/>
+      <c r="E84" s="83"/>
+      <c r="F84" s="83"/>
+      <c r="G84" s="83"/>
+      <c r="H84" s="145">
+        <f>Planilla!G32</f>
+        <v>3136024.996325769</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="79" t="s">
+        <v>149</v>
+      </c>
+      <c r="B85" s="80"/>
+      <c r="C85" s="80"/>
+      <c r="D85" s="80"/>
+      <c r="E85" s="80"/>
+      <c r="F85" s="80"/>
+      <c r="G85" s="80"/>
+      <c r="H85" s="69">
+        <f>-(H76)</f>
+        <v>-1859131.45</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="79" t="s">
         <v>88</v>
       </c>
-      <c r="B71" s="218"/>
-      <c r="C71" s="218"/>
-      <c r="D71" s="218"/>
-      <c r="E71" s="218"/>
-      <c r="F71" s="218"/>
-      <c r="G71" s="218"/>
-      <c r="H71" s="169"/>
-    </row>
-    <row r="72" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A72" s="226" t="s">
-        <v>153</v>
-      </c>
-      <c r="B72" s="227"/>
-      <c r="C72" s="227"/>
-      <c r="D72" s="227"/>
-      <c r="E72" s="227"/>
-      <c r="F72" s="227"/>
-      <c r="G72" s="228"/>
-      <c r="H72" s="74">
-        <f>19000+81000</f>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A73" s="131" t="s">
-        <v>77</v>
-      </c>
-      <c r="B73" s="81"/>
-      <c r="C73" s="81"/>
-      <c r="D73" s="81"/>
-      <c r="E73" s="81"/>
-      <c r="F73" s="81"/>
-      <c r="G73" s="81"/>
-      <c r="H73" s="70">
-        <f>SUM(H72:H72)</f>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A74" s="132"/>
-      <c r="B74" s="132"/>
-      <c r="C74" s="132"/>
-      <c r="D74" s="132"/>
-      <c r="E74" s="132"/>
-      <c r="F74" s="132"/>
-      <c r="G74" s="132"/>
-      <c r="H74" s="133"/>
-    </row>
-    <row r="75" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A75" s="199" t="s">
-        <v>87</v>
-      </c>
-      <c r="B75" s="200"/>
-      <c r="C75" s="200"/>
-      <c r="D75" s="200"/>
-      <c r="E75" s="200"/>
-      <c r="F75" s="200"/>
-      <c r="G75" s="200"/>
-      <c r="H75" s="134">
-        <f>H73</f>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A76" s="211" t="s">
-        <v>95</v>
-      </c>
-      <c r="B76" s="212"/>
-      <c r="C76" s="212"/>
-      <c r="D76" s="212"/>
-      <c r="E76" s="212"/>
-      <c r="F76" s="212"/>
-      <c r="G76" s="213"/>
-      <c r="H76" s="134"/>
-    </row>
-    <row r="77" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A77" s="211" t="s">
-        <v>100</v>
-      </c>
-      <c r="B77" s="212"/>
-      <c r="C77" s="212"/>
-      <c r="D77" s="212"/>
-      <c r="E77" s="212"/>
-      <c r="F77" s="212"/>
-      <c r="G77" s="213"/>
-      <c r="H77" s="134">
-        <v>1700000</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="18.75">
-      <c r="A78" s="199" t="s">
-        <v>96</v>
-      </c>
-      <c r="B78" s="200"/>
-      <c r="C78" s="200"/>
-      <c r="D78" s="200"/>
-      <c r="E78" s="200"/>
-      <c r="F78" s="200"/>
-      <c r="G78" s="200"/>
-      <c r="H78" s="134">
-        <f>H33+H42+H50+H55+H58+H38+H21+H29</f>
-        <v>2090498.8599999999</v>
-      </c>
-      <c r="J78" s="7"/>
-      <c r="K78" s="146"/>
-    </row>
-    <row r="79" spans="1:11" ht="18.75">
-      <c r="A79" s="208" t="s">
-        <v>130</v>
-      </c>
-      <c r="B79" s="209"/>
-      <c r="C79" s="209"/>
-      <c r="D79" s="209"/>
-      <c r="E79" s="209"/>
-      <c r="F79" s="209"/>
-      <c r="G79" s="210"/>
-      <c r="H79" s="135">
-        <f>H76+H78</f>
-        <v>2090498.8599999999</v>
-      </c>
-      <c r="I79" s="130"/>
-      <c r="J79" s="189"/>
-      <c r="K79" s="189"/>
-    </row>
-    <row r="80" spans="1:11" ht="18.75">
-      <c r="A80" s="208" t="s">
+      <c r="B86" s="80"/>
+      <c r="C86" s="80"/>
+      <c r="D86" s="80"/>
+      <c r="E86" s="80"/>
+      <c r="F86" s="80"/>
+      <c r="G86" s="80"/>
+      <c r="H86" s="69">
+        <f>-H63</f>
+        <v>0</v>
+      </c>
+      <c r="K86" s="6"/>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" s="79" t="s">
+        <v>73</v>
+      </c>
+      <c r="B87" s="80" t="s">
+        <v>118</v>
+      </c>
+      <c r="C87" s="80"/>
+      <c r="D87" s="80"/>
+      <c r="E87" s="80"/>
+      <c r="F87" s="80"/>
+      <c r="G87" s="80"/>
+      <c r="H87" s="125">
+        <v>115393.04</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" s="79" t="s">
+        <v>72</v>
+      </c>
+      <c r="B88" s="80"/>
+      <c r="C88" s="80"/>
+      <c r="D88" s="80"/>
+      <c r="E88" s="80"/>
+      <c r="F88" s="80"/>
+      <c r="G88" s="80"/>
+      <c r="H88" s="125">
+        <v>36320.800000000003</v>
+      </c>
+      <c r="I88" s="146"/>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B89" s="84"/>
+      <c r="C89" s="4"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="4"/>
+      <c r="H89" s="99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="18.75">
+      <c r="A90" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B90" s="23"/>
+      <c r="C90" s="23"/>
+      <c r="D90" s="23"/>
+      <c r="E90" s="23"/>
+      <c r="F90" s="23"/>
+      <c r="G90" s="23"/>
+      <c r="H90" s="85">
+        <f>SUM(H83:H89)</f>
+        <v>4583896.9266090551</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="15.75" thickBot="1"/>
+    <row r="92" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A92" s="191" t="s">
         <v>101</v>
       </c>
-      <c r="B80" s="209"/>
-      <c r="C80" s="209"/>
-      <c r="D80" s="209"/>
-      <c r="E80" s="209"/>
-      <c r="F80" s="209"/>
-      <c r="G80" s="210"/>
-      <c r="H80" s="136">
-        <f>H77+H75</f>
-        <v>1800000</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A81" s="214" t="s">
-        <v>89</v>
-      </c>
-      <c r="B81" s="215"/>
-      <c r="C81" s="215"/>
-      <c r="D81" s="215"/>
-      <c r="E81" s="215"/>
-      <c r="F81" s="215"/>
-      <c r="G81" s="215"/>
-      <c r="H81" s="137">
-        <f>H78+H75</f>
-        <v>2190498.86</v>
-      </c>
-      <c r="J81" s="7"/>
-    </row>
-    <row r="82" spans="1:11" ht="18.75" hidden="1">
-      <c r="A82" s="201" t="s">
-        <v>17</v>
-      </c>
-      <c r="B82" s="202"/>
-      <c r="C82" s="202"/>
-      <c r="D82" s="202"/>
-      <c r="E82" s="202"/>
-      <c r="F82" s="202"/>
-      <c r="G82" s="202"/>
-      <c r="H82" s="138">
-        <f>H67</f>
-        <v>0</v>
-      </c>
-      <c r="J82" s="7"/>
-    </row>
-    <row r="83" spans="1:11" ht="18.75" hidden="1">
-      <c r="A83" s="139"/>
-      <c r="B83" s="139"/>
-      <c r="C83" s="139"/>
-      <c r="D83" s="139"/>
-      <c r="E83" s="139"/>
-      <c r="F83" s="139"/>
-      <c r="G83" s="139"/>
-      <c r="H83" s="140"/>
-      <c r="J83" s="7"/>
-    </row>
-    <row r="84" spans="1:11" ht="18.75" hidden="1">
-      <c r="A84" s="139"/>
-      <c r="B84" s="139"/>
-      <c r="C84" s="139"/>
-      <c r="D84" s="139"/>
-      <c r="E84" s="139"/>
-      <c r="F84" s="139"/>
-      <c r="G84" s="139"/>
-      <c r="H84" s="140"/>
-      <c r="J84" s="7"/>
-    </row>
-    <row r="85" spans="1:11" ht="18.75" hidden="1">
-      <c r="A85" s="139"/>
-      <c r="B85" s="139"/>
-      <c r="C85" s="139"/>
-      <c r="D85" s="139"/>
-      <c r="E85" s="139"/>
-      <c r="F85" s="139"/>
-      <c r="G85" s="139"/>
-      <c r="H85" s="140"/>
-      <c r="J85" s="7"/>
-    </row>
-    <row r="86" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A86" s="141"/>
-      <c r="B86" s="141"/>
-      <c r="C86" s="141"/>
-      <c r="D86" s="141"/>
-      <c r="E86" s="141"/>
-      <c r="F86" s="141"/>
-      <c r="G86" s="141"/>
-      <c r="H86" s="141"/>
-    </row>
-    <row r="87" spans="1:11" ht="18.75">
-      <c r="A87" s="194" t="s">
-        <v>10</v>
-      </c>
-      <c r="B87" s="195"/>
-      <c r="C87" s="195"/>
-      <c r="D87" s="195"/>
-      <c r="E87" s="195"/>
-      <c r="F87" s="195"/>
-      <c r="G87" s="195"/>
-      <c r="H87" s="196"/>
-    </row>
-    <row r="88" spans="1:11" ht="18.75">
-      <c r="A88" s="142" t="s">
+      <c r="B92" s="192"/>
+      <c r="C92" s="192"/>
+      <c r="D92" s="192"/>
+      <c r="E92" s="192"/>
+      <c r="F92" s="192"/>
+      <c r="G92" s="192"/>
+      <c r="H92" s="193"/>
+    </row>
+    <row r="93" spans="1:11" ht="15.75">
+      <c r="A93" s="88" t="s">
         <v>12</v>
       </c>
-      <c r="B88" s="143"/>
-      <c r="C88" s="143"/>
-      <c r="D88" s="143"/>
-      <c r="E88" s="143"/>
-      <c r="F88" s="143"/>
-      <c r="G88" s="143"/>
-      <c r="H88" s="144">
-        <v>839961.22447473579</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11">
-      <c r="A89" s="82" t="s">
-        <v>140</v>
-      </c>
-      <c r="B89" s="83"/>
-      <c r="C89" s="83"/>
-      <c r="D89" s="83"/>
-      <c r="E89" s="83"/>
-      <c r="F89" s="83"/>
-      <c r="G89" s="83"/>
-      <c r="H89" s="145">
-        <f>Planilla!G32</f>
-        <v>4651785.9958085511</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11">
-      <c r="A90" s="79" t="s">
-        <v>159</v>
-      </c>
-      <c r="B90" s="80"/>
-      <c r="C90" s="80"/>
-      <c r="D90" s="80"/>
-      <c r="E90" s="80"/>
-      <c r="F90" s="80"/>
-      <c r="G90" s="80"/>
-      <c r="H90" s="69">
-        <f>-(H81)</f>
-        <v>-2190498.86</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11">
-      <c r="A91" s="79" t="s">
-        <v>90</v>
-      </c>
-      <c r="B91" s="80"/>
-      <c r="C91" s="80"/>
-      <c r="D91" s="80"/>
-      <c r="E91" s="80"/>
-      <c r="F91" s="80"/>
-      <c r="G91" s="80"/>
-      <c r="H91" s="69">
-        <f>-H68</f>
-        <v>-100000</v>
-      </c>
-      <c r="K91" s="181" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11">
-      <c r="A92" s="79" t="s">
-        <v>75</v>
-      </c>
-      <c r="B92" s="80" t="s">
-        <v>122</v>
-      </c>
-      <c r="C92" s="80"/>
-      <c r="D92" s="80"/>
-      <c r="E92" s="80"/>
-      <c r="F92" s="80"/>
-      <c r="G92" s="80"/>
-      <c r="H92" s="125">
-        <v>115393.04</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11">
-      <c r="A93" s="79" t="s">
-        <v>74</v>
-      </c>
-      <c r="B93" s="80"/>
-      <c r="C93" s="80"/>
-      <c r="D93" s="80"/>
-      <c r="E93" s="80"/>
-      <c r="F93" s="80"/>
-      <c r="G93" s="80"/>
-      <c r="H93" s="125">
-        <v>36320.800000000003</v>
-      </c>
-      <c r="I93" s="146"/>
+      <c r="B93" s="88"/>
+      <c r="C93" s="88"/>
+      <c r="D93" s="88"/>
+      <c r="E93" s="88"/>
+      <c r="F93" s="88"/>
+      <c r="G93" s="88"/>
+      <c r="H93" s="89">
+        <v>0</v>
+      </c>
     </row>
     <row r="94" spans="1:11">
-      <c r="A94" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="B94" s="84"/>
+      <c r="A94" s="61" t="s">
+        <v>125</v>
+      </c>
+      <c r="B94" s="92"/>
       <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" ht="18.75">
-      <c r="A95" s="22" t="s">
+      <c r="D94" s="61"/>
+      <c r="E94" s="61"/>
+      <c r="F94" s="61"/>
+      <c r="G94" s="61"/>
+      <c r="H94" s="129"/>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="61"/>
+      <c r="B95" s="98"/>
+      <c r="C95" s="61"/>
+      <c r="D95" s="61"/>
+      <c r="E95" s="61"/>
+      <c r="F95" s="61"/>
+      <c r="G95" s="61"/>
+      <c r="H95" s="21"/>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" s="61"/>
+      <c r="B96" s="61"/>
+      <c r="C96" s="61"/>
+      <c r="D96" s="61"/>
+      <c r="E96" s="61"/>
+      <c r="F96" s="61"/>
+      <c r="G96" s="61"/>
+      <c r="H96" s="21"/>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="86" t="s">
         <v>11</v>
       </c>
-      <c r="B95" s="23"/>
-      <c r="C95" s="23"/>
-      <c r="D95" s="23"/>
-      <c r="E95" s="23"/>
-      <c r="F95" s="23"/>
-      <c r="G95" s="23"/>
-      <c r="H95" s="85">
-        <f>SUM(H88:H94)</f>
-        <v>3352962.2002832866</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" ht="15.75" thickBot="1"/>
-    <row r="97" spans="1:8" ht="16.5" thickBot="1">
-      <c r="A97" s="191" t="s">
-        <v>105</v>
-      </c>
-      <c r="B97" s="192"/>
-      <c r="C97" s="192"/>
-      <c r="D97" s="192"/>
-      <c r="E97" s="192"/>
-      <c r="F97" s="192"/>
-      <c r="G97" s="192"/>
-      <c r="H97" s="193"/>
-    </row>
-    <row r="98" spans="1:8" ht="15.75">
-      <c r="A98" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="B98" s="88"/>
-      <c r="C98" s="88"/>
-      <c r="D98" s="88"/>
-      <c r="E98" s="88"/>
-      <c r="F98" s="88"/>
-      <c r="G98" s="88"/>
-      <c r="H98" s="89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8">
-      <c r="A99" s="61" t="s">
-        <v>129</v>
-      </c>
-      <c r="B99" s="92"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="61"/>
-      <c r="E99" s="61"/>
-      <c r="F99" s="61"/>
-      <c r="G99" s="61"/>
-      <c r="H99" s="129"/>
-    </row>
-    <row r="100" spans="1:8">
-      <c r="A100" s="61"/>
-      <c r="B100" s="98"/>
-      <c r="C100" s="61"/>
-      <c r="D100" s="61"/>
-      <c r="E100" s="61"/>
-      <c r="F100" s="61"/>
-      <c r="G100" s="61"/>
-      <c r="H100" s="21"/>
-    </row>
-    <row r="101" spans="1:8">
-      <c r="A101" s="61"/>
-      <c r="B101" s="61"/>
-      <c r="C101" s="61"/>
-      <c r="D101" s="61"/>
-      <c r="E101" s="61"/>
-      <c r="F101" s="61"/>
-      <c r="G101" s="61"/>
-      <c r="H101" s="21"/>
-    </row>
-    <row r="102" spans="1:8">
-      <c r="A102" s="86" t="s">
-        <v>11</v>
-      </c>
-      <c r="B102" s="86"/>
-      <c r="C102" s="86"/>
-      <c r="D102" s="86"/>
-      <c r="E102" s="86"/>
-      <c r="F102" s="86"/>
-      <c r="G102" s="86"/>
-      <c r="H102" s="87">
-        <f>SUM(H98:H101)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" hidden="1">
-      <c r="A105" s="190"/>
-      <c r="B105" s="190"/>
-      <c r="C105" s="190"/>
-      <c r="D105" s="190"/>
-      <c r="E105" s="190"/>
-      <c r="F105" s="190"/>
-      <c r="G105" s="190"/>
-      <c r="H105" s="190"/>
-    </row>
-    <row r="106" spans="1:8" hidden="1">
-      <c r="A106" s="190"/>
-      <c r="B106" s="190"/>
-      <c r="C106" s="190"/>
-      <c r="D106" s="190"/>
-      <c r="E106" s="190"/>
-      <c r="F106" s="190"/>
-      <c r="G106" s="190"/>
-      <c r="H106" s="190"/>
-    </row>
-    <row r="107" spans="1:8" hidden="1">
-      <c r="A107" s="190"/>
-      <c r="B107" s="190"/>
-      <c r="C107" s="190"/>
-      <c r="D107" s="190"/>
-      <c r="E107" s="190"/>
-      <c r="F107" s="190"/>
-      <c r="G107" s="190"/>
-      <c r="H107" s="190"/>
-    </row>
-    <row r="108" spans="1:8" hidden="1">
-      <c r="A108" s="190"/>
-      <c r="B108" s="190"/>
-      <c r="C108" s="190"/>
-      <c r="D108" s="190"/>
-      <c r="E108" s="190"/>
-      <c r="F108" s="190"/>
-      <c r="G108" s="190"/>
-      <c r="H108" s="190"/>
+      <c r="B97" s="86"/>
+      <c r="C97" s="86"/>
+      <c r="D97" s="86"/>
+      <c r="E97" s="86"/>
+      <c r="F97" s="86"/>
+      <c r="G97" s="86"/>
+      <c r="H97" s="87">
+        <f>SUM(H93:H96)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" hidden="1">
+      <c r="A100" s="190"/>
+      <c r="B100" s="190"/>
+      <c r="C100" s="190"/>
+      <c r="D100" s="190"/>
+      <c r="E100" s="190"/>
+      <c r="F100" s="190"/>
+      <c r="G100" s="190"/>
+      <c r="H100" s="190"/>
+    </row>
+    <row r="101" spans="1:8" hidden="1">
+      <c r="A101" s="190"/>
+      <c r="B101" s="190"/>
+      <c r="C101" s="190"/>
+      <c r="D101" s="190"/>
+      <c r="E101" s="190"/>
+      <c r="F101" s="190"/>
+      <c r="G101" s="190"/>
+      <c r="H101" s="190"/>
+    </row>
+    <row r="102" spans="1:8" hidden="1">
+      <c r="A102" s="190"/>
+      <c r="B102" s="190"/>
+      <c r="C102" s="190"/>
+      <c r="D102" s="190"/>
+      <c r="E102" s="190"/>
+      <c r="F102" s="190"/>
+      <c r="G102" s="190"/>
+      <c r="H102" s="190"/>
+    </row>
+    <row r="103" spans="1:8" hidden="1">
+      <c r="A103" s="190"/>
+      <c r="B103" s="190"/>
+      <c r="C103" s="190"/>
+      <c r="D103" s="190"/>
+      <c r="E103" s="190"/>
+      <c r="F103" s="190"/>
+      <c r="G103" s="190"/>
+      <c r="H103" s="190"/>
     </row>
   </sheetData>
   <mergeCells count="29">
     <mergeCell ref="D2:H2"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A64:H65"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="A100:H103"/>
+    <mergeCell ref="A92:H92"/>
+    <mergeCell ref="A82:H82"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="A73:G73"/>
     <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A81:G81"/>
-    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A59:H59"/>
     <mergeCell ref="A75:G75"/>
     <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A69:H70"/>
-    <mergeCell ref="J79:K79"/>
-    <mergeCell ref="A105:H108"/>
-    <mergeCell ref="A97:H97"/>
-    <mergeCell ref="A87:H87"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="A82:G82"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A64:H64"/>
-    <mergeCell ref="A80:G80"/>
-    <mergeCell ref="A76:G76"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
